--- a/downloads/agent-run-cost-model.xlsx
+++ b/downloads/agent-run-cost-model.xlsx
@@ -2427,7 +2427,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>The team built a full agent that reads the request, checks stock and supplier terms, and places the order. It worked. It also cost more to run each month than the buyers did.</t>
+          <t>The team built a full agent that reads the request, checks stock and supplier terms, and places the order. It worked. It ran at ₹3.7L a month against ₹5L for the buyers, and still lost money over the year once the ₹23L build and the upkeep were counted.</t>
         </is>
       </c>
     </row>

--- a/downloads/agent-run-cost-model.xlsx
+++ b/downloads/agent-run-cost-model.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Your model" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Reference example" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Your model" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference example" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Your model'!$7:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Reference example'!$14:$15</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,75 +33,80 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Helvetica Neue"/>
-      <b val="1"/>
-      <color rgb="00FFC123"/>
-      <sz val="11"/>
+      <name val="Source Serif 4"/>
+      <color rgb="00183D32"/>
+      <sz val="22"/>
     </font>
     <font>
-      <name val="Helvetica Neue"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="Helvetica Neue"/>
-      <color rgb="00A3ACB8"/>
+      <name val="Figtree"/>
+      <color rgb="00526259"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Helvetica Neue"/>
+      <name val="Figtree"/>
       <b val="1"/>
-      <color rgb="0016212E"/>
+      <color rgb="00183D32"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Helvetica Neue"/>
-      <color rgb="0016212E"/>
+      <name val="Figtree"/>
+      <color rgb="00172E26"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Helvetica Neue"/>
+      <name val="Figtree"/>
       <b val="1"/>
-      <color rgb="0016212E"/>
+      <color rgb="00172E26"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Helvetica Neue"/>
+      <name val="Figtree"/>
       <b val="1"/>
-      <color rgb="005F6B78"/>
+      <color rgb="00526259"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Helvetica Neue"/>
-      <color rgb="005F6B78"/>
+      <name val="Figtree"/>
+      <color rgb="00526259"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Helvetica Neue"/>
+      <name val="Source Serif 4"/>
       <b val="1"/>
-      <color rgb="0016212E"/>
+      <color rgb="00F5F0E6"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Figtree"/>
+      <color rgb="00F5F0E6"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Figtree"/>
+      <b val="1"/>
+      <color rgb="00F5F0E6"/>
       <sz val="10"/>
       <u val="single"/>
     </font>
     <font>
-      <name val="Helvetica Neue"/>
-      <color rgb="005F6B78"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Helvetica Neue"/>
-      <color rgb="005F6B78"/>
+      <name val="Figtree"/>
+      <color rgb="00526259"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Helvetica Neue"/>
+      <name val="Figtree"/>
       <b val="1"/>
-      <color rgb="0016212E"/>
+      <color rgb="00183D32"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Figtree"/>
+      <b val="1"/>
+      <color rgb="00172E26"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -106,28 +114,37 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="solid"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC123"/>
-        <bgColor rgb="00FFC123"/>
+        <fgColor rgb="00F4E9CE"/>
+        <bgColor rgb="00F4E9CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F3F5"/>
-        <bgColor rgb="00F1F3F5"/>
+        <fgColor rgb="00E5EBE1"/>
+        <bgColor rgb="00E5EBE1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FD8549"/>
-        <bgColor rgb="00FD8549"/>
+        <fgColor rgb="00183D32"/>
+        <bgColor rgb="00183D32"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F0E6"/>
+        <bgColor rgb="00F5F0E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBF8F2"/>
+        <bgColor rgb="00FBF8F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -135,71 +152,93 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00B58A46"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD1C8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD1C8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD1C8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD1C8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -274,6 +313,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2000250" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2000250" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2000250" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -562,23 +691,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00183D32"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A62"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>● The Living Craft</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>The Run-Cost Model Tool</t>
@@ -592,6 +718,9 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="1" t="n"/>
+    </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -627,6 +756,9 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+    </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -637,7 +769,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>1. Open the sheet called Your model. Fill the yellow cells. Column C says what to type and where the number comes from.</t>
+          <t>1. Open the sheet called Your model. Fill the sand-coloured cells. Column C says what to type and where the number comes from.</t>
         </is>
       </c>
     </row>
@@ -658,14 +790,14 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>4. Grey rows are worked out for you. Do not type into them.</t>
+          <t>4. Pale green rows are worked out for you. Do not type into them.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>5. Excel treats a blank cell as 0, so a half-filled sheet shows a number that is not a result. The page at the link below keeps the result off the screen until every line is set; here, fill every yellow cell before you read the totals.</t>
+          <t>5. Excel treats a blank cell as 0, so a half-filled sheet shows a number that is not a result. The page at the link below keeps the result off the screen until every line is set; here, fill every sand-coloured cell before you read the totals.</t>
         </is>
       </c>
     </row>
@@ -683,6 +815,9 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+    </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
@@ -693,14 +828,14 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Yellow: a cell you fill in.</t>
+          <t>Sand: a cell you fill in.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Grey: a line the sheet works out. Do not type into it.</t>
+          <t>Pale green: a line the sheet works out. Do not type into it.</t>
         </is>
       </c>
     </row>
@@ -711,6 +846,9 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+    </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
@@ -753,6 +891,9 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="1" t="n"/>
+    </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
@@ -795,6 +936,9 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="1" t="n"/>
+    </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
@@ -844,6 +988,9 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="1" t="n"/>
+    </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
@@ -858,6 +1005,9 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="1" t="n"/>
+    </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
@@ -893,6 +1043,9 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="1" t="n"/>
+    </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
@@ -928,28 +1081,41 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="1" t="n"/>
+    </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="12" t="inlineStr">
         <is>
           <t>The Run-Cost Model Tool · The Living Craft · Built by Sunil Mathew, co-authored with Claude · free to use and to pass on</t>
         </is>
       </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId1"/>
   </hyperlinks>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00183D32"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -961,20 +1127,16 @@
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>● The Living Craft</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="n"/>
-      <c r="C1" s="13" t="n"/>
-      <c r="D1" s="13" t="n"/>
-      <c r="E1" s="13" t="n"/>
-      <c r="F1" s="13" t="n"/>
-      <c r="G1" s="13" t="n"/>
-    </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>The Run-Cost Model Tool</t>
@@ -993,19 +1155,43 @@
           <t>Four ways to do the same job, costed over one period  ·  Built by Sunil Mathew, co-authored with Claude</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n"/>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="13" t="n"/>
-      <c r="G3" s="13" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="n"/>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="1" t="n"/>
+      <c r="F4" s="1" t="n"/>
+      <c r="G4" s="1" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Fill the yellow cells. Column C says what to type and where the number comes from. Grey rows are worked out for you; do not type into them. Percent lines take a percentage: 12 means 12%.</t>
-        </is>
-      </c>
+          <t>Fill the sand-coloured cells. Column C says what to type and where the number comes from. Pale green rows are worked out for you; do not type into them. Percent lines take a percentage: 12 means 12%.</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+      <c r="E5" s="1" t="n"/>
+      <c r="F5" s="1" t="n"/>
+      <c r="G5" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="1" t="n"/>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="1" t="n"/>
+      <c r="G6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
@@ -1045,6 +1231,9 @@
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
       <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Plain code, from the rules the team already knew.</t>
@@ -1089,7 +1278,7 @@
           <t>Currency label</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>free text</t>
         </is>
@@ -1100,6 +1289,9 @@
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
+      <c r="E10" s="1" t="n"/>
+      <c r="F10" s="1" t="n"/>
+      <c r="G10" s="1" t="n"/>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1117,7 +1309,10 @@
           <t>One case is one unit of work: a purchase order, a ticket, a refund request. Take the count from last quarter, not from the plan.</t>
         </is>
       </c>
-      <c r="D11" s="21" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="1" t="n"/>
+      <c r="F11" s="1" t="n"/>
+      <c r="G11" s="1" t="n"/>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1135,7 +1330,10 @@
           <t>The window the build has to pay for itself. Twelve is the usual budget horizon. Make it longer only if you can defend the longer horizon in the room.</t>
         </is>
       </c>
-      <c r="D12" s="21" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1153,7 +1351,10 @@
           <t>How long one person takes to finish one case today. Time it on ten real cases.</t>
         </is>
       </c>
-      <c r="D13" s="21" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="1" t="n"/>
+      <c r="F13" s="1" t="n"/>
+      <c r="G13" s="1" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1171,55 +1372,67 @@
           <t>Fully loaded: salary, benefits, seat. Use the rate of the people who actually do the work today.</t>
         </is>
       </c>
-      <c r="D14" s="21" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="1" t="n"/>
+      <c r="F14" s="1" t="n"/>
+      <c r="G14" s="1" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>Total cases in the period</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>Cases per month multiplied by months.</t>
         </is>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="24">
         <f>$D$11*$D$12</f>
         <v/>
       </c>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="18" t="n"/>
-      <c r="G15" s="18" t="n"/>
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="25" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>Manual baseline cost for the period</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>Total cases, times minutes per case, times the hourly rate. This is the number every option has to beat.</t>
         </is>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="24">
         <f>$D$15*$D$13/60*$D$14</f>
         <v/>
       </c>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="18" t="n"/>
-      <c r="G16" s="18" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="n"/>
+      <c r="C17" s="1" t="n"/>
+      <c r="D17" s="1" t="n"/>
+      <c r="E17" s="1" t="n"/>
+      <c r="F17" s="1" t="n"/>
+      <c r="G17" s="1" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="17" t="inlineStr">
@@ -1254,7 +1467,10 @@
           <t>What one engineer-day costs you. Used for the build and for upkeep.</t>
         </is>
       </c>
-      <c r="D19" s="21" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="1" t="n"/>
+      <c r="F19" s="1" t="n"/>
+      <c r="G19" s="1" t="n"/>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -1272,7 +1488,10 @@
           <t>Used for escalations: the cases an engineer has to look at.</t>
         </is>
       </c>
-      <c r="D20" s="21" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="1" t="n"/>
+      <c r="F20" s="1" t="n"/>
+      <c r="G20" s="1" t="n"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -1290,7 +1509,19 @@
           <t>Used for reviewing output and for finishing declined cases by hand. Often the same rate as the manual baseline.</t>
         </is>
       </c>
-      <c r="D21" s="21" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="1" t="n"/>
+      <c r="F21" s="1" t="n"/>
+      <c r="G21" s="1" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="1" t="n"/>
+      <c r="D22" s="1" t="n"/>
+      <c r="E22" s="1" t="n"/>
+      <c r="F22" s="1" t="n"/>
+      <c r="G22" s="1" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="17" t="inlineStr">
@@ -1325,10 +1556,10 @@
           <t>From the first line of code to a system that handles real cases. Include integration with the tools it calls.</t>
         </is>
       </c>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="21" t="n"/>
-      <c r="G24" s="21" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="20" t="n"/>
+      <c r="F24" s="20" t="n"/>
+      <c r="G24" s="20" t="n"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -1346,43 +1577,52 @@
           <t>An eval is a set of real cases with known-correct answers that the system is scored against. Building one is engineering time.</t>
         </is>
       </c>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="21" t="n"/>
-      <c r="F25" s="21" t="n"/>
-      <c r="G25" s="21" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="20" t="n"/>
+      <c r="F25" s="20" t="n"/>
+      <c r="G25" s="20" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>Total build cost</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>Build days plus eval days, times the engineering day rate.</t>
         </is>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="24">
         <f>(D24+D25)*$D$19</f>
         <v/>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="24">
         <f>(E24+E25)*$D$19</f>
         <v/>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="24">
         <f>(F24+F25)*$D$19</f>
         <v/>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="24">
         <f>(G24+G25)*$D$19</f>
         <v/>
       </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="1" t="n"/>
+      <c r="C27" s="1" t="n"/>
+      <c r="D27" s="1" t="n"/>
+      <c r="E27" s="1" t="n"/>
+      <c r="F27" s="1" t="n"/>
+      <c r="G27" s="1" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
@@ -1417,10 +1657,10 @@
           <t>How many times a case calls the model when everything works. An agent that plans, then acts, then checks its work makes several.</t>
         </is>
       </c>
-      <c r="D29" s="21" t="n"/>
-      <c r="E29" s="21" t="n"/>
-      <c r="F29" s="21" t="n"/>
-      <c r="G29" s="21" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
+      <c r="F29" s="20" t="n"/>
+      <c r="G29" s="20" t="n"/>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
@@ -1438,10 +1678,10 @@
           <t>Total model calls divided by successful ones. Count timeouts, tool errors and loops that re-enter, not only refusals. 1.0 means the system never retries, which no real system does.</t>
         </is>
       </c>
-      <c r="D30" s="21" t="n"/>
-      <c r="E30" s="21" t="n"/>
-      <c r="F30" s="21" t="n"/>
-      <c r="G30" s="21" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
+      <c r="F30" s="20" t="n"/>
+      <c r="G30" s="20" t="n"/>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -1459,10 +1699,10 @@
           <t>Average cost of one call, including the input tokens. Take it from a month of real invoices, not from the price list.</t>
         </is>
       </c>
-      <c r="D31" s="21" t="n"/>
-      <c r="E31" s="21" t="n"/>
-      <c r="F31" s="21" t="n"/>
-      <c r="G31" s="21" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
+      <c r="F31" s="20" t="n"/>
+      <c r="G31" s="20" t="n"/>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -1480,10 +1720,10 @@
           <t>Lookups, searches, writes to other systems. Anything with a price per call or a rate limit.</t>
         </is>
       </c>
-      <c r="D32" s="21" t="n"/>
-      <c r="E32" s="21" t="n"/>
-      <c r="F32" s="21" t="n"/>
-      <c r="G32" s="21" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="20" t="n"/>
+      <c r="F32" s="20" t="n"/>
+      <c r="G32" s="20" t="n"/>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -1501,76 +1741,85 @@
           <t>Average across the tools it calls. Internal calls are not free: price the compute.</t>
         </is>
       </c>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
-      <c r="F33" s="21" t="n"/>
-      <c r="G33" s="21" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="20" t="n"/>
+      <c r="F33" s="20" t="n"/>
+      <c r="G33" s="20" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>Model cost per month</t>
         </is>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>Cases per month, times calls per case, times the retry multiplier, times the cost per call.</t>
         </is>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="24">
         <f>$D$11*D29*D30*D31</f>
         <v/>
       </c>
-      <c r="E34" s="25">
+      <c r="E34" s="24">
         <f>$D$11*E29*E30*E31</f>
         <v/>
       </c>
-      <c r="F34" s="25">
+      <c r="F34" s="24">
         <f>$D$11*F29*F30*F31</f>
         <v/>
       </c>
-      <c r="G34" s="25">
+      <c r="G34" s="24">
         <f>$D$11*G29*G30*G31</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>Tool cost per month</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>Cases per month, times tool calls per case, times the cost per tool call.</t>
         </is>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="24">
         <f>$D$11*D32*D33</f>
         <v/>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="24">
         <f>$D$11*E32*E33</f>
         <v/>
       </c>
-      <c r="F35" s="25">
+      <c r="F35" s="24">
         <f>$D$11*F32*F33</f>
         <v/>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="24">
         <f>$D$11*G32*G33</f>
         <v/>
       </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="1" t="n"/>
+      <c r="C36" s="1" t="n"/>
+      <c r="D36" s="1" t="n"/>
+      <c r="E36" s="1" t="n"/>
+      <c r="F36" s="1" t="n"/>
+      <c r="G36" s="1" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="17" t="inlineStr">
@@ -1605,10 +1854,10 @@
           <t>100 for a model-assisted draft, because a person approves every one. A sample, such as 20, for a full agent.</t>
         </is>
       </c>
-      <c r="D38" s="21" t="n"/>
-      <c r="E38" s="21" t="n"/>
-      <c r="F38" s="21" t="n"/>
-      <c r="G38" s="21" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="20" t="n"/>
+      <c r="F38" s="20" t="n"/>
+      <c r="G38" s="20" t="n"/>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
@@ -1626,10 +1875,10 @@
           <t>Time it on real cases. Approving a good draft is quick; checking an agent that acted on its own is not.</t>
         </is>
       </c>
-      <c r="D39" s="21" t="n"/>
-      <c r="E39" s="21" t="n"/>
-      <c r="F39" s="21" t="n"/>
-      <c r="G39" s="21" t="n"/>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="n"/>
+      <c r="F39" s="20" t="n"/>
+      <c r="G39" s="20" t="n"/>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
@@ -1647,10 +1896,10 @@
           <t>Cases that stop and need somebody who can read the trace. Measure it in a trial. A demo will show you 0.</t>
         </is>
       </c>
-      <c r="D40" s="21" t="n"/>
-      <c r="E40" s="21" t="n"/>
-      <c r="F40" s="21" t="n"/>
-      <c r="G40" s="21" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="20" t="n"/>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
@@ -1668,10 +1917,10 @@
           <t>Reading the trace, working out what happened, fixing the case. Longer for an agent, because there is more trace to read.</t>
         </is>
       </c>
-      <c r="D41" s="21" t="n"/>
-      <c r="E41" s="21" t="n"/>
-      <c r="F41" s="21" t="n"/>
-      <c r="G41" s="21" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="20" t="n"/>
+      <c r="G41" s="20" t="n"/>
     </row>
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
@@ -1689,10 +1938,10 @@
           <t>Cases the system refuses or gives up on. They do not disappear: a person finishes them, at the manual rate.</t>
         </is>
       </c>
-      <c r="D42" s="21" t="n"/>
-      <c r="E42" s="21" t="n"/>
-      <c r="F42" s="21" t="n"/>
-      <c r="G42" s="21" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="20" t="n"/>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -1710,109 +1959,118 @@
           <t>Usually close to the manual baseline, because the person starts from nothing.</t>
         </is>
       </c>
-      <c r="D43" s="21" t="n"/>
-      <c r="E43" s="21" t="n"/>
-      <c r="F43" s="21" t="n"/>
-      <c r="G43" s="21" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="20" t="n"/>
+      <c r="F43" s="20" t="n"/>
+      <c r="G43" s="20" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="22" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>Review cost per month</t>
         </is>
       </c>
-      <c r="B44" s="23" t="inlineStr">
+      <c r="B44" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C44" s="24" t="inlineStr">
+      <c r="C44" s="23" t="inlineStr">
         <is>
           <t>Cases per month, times the share reviewed, times minutes per review, at the reviewer rate.</t>
         </is>
       </c>
-      <c r="D44" s="25">
+      <c r="D44" s="24">
         <f>$D$11*D38/100*D39/60*$D$21</f>
         <v/>
       </c>
-      <c r="E44" s="25">
+      <c r="E44" s="24">
         <f>$D$11*E38/100*E39/60*$D$21</f>
         <v/>
       </c>
-      <c r="F44" s="25">
+      <c r="F44" s="24">
         <f>$D$11*F38/100*F39/60*$D$21</f>
         <v/>
       </c>
-      <c r="G44" s="25">
+      <c r="G44" s="24">
         <f>$D$11*G38/100*G39/60*$D$21</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="22" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>Escalation cost per month</t>
         </is>
       </c>
-      <c r="B45" s="23" t="inlineStr">
+      <c r="B45" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C45" s="24" t="inlineStr">
+      <c r="C45" s="23" t="inlineStr">
         <is>
           <t>Cases per month, times the share escalated, times minutes per escalation, at the engineer rate.</t>
         </is>
       </c>
-      <c r="D45" s="25">
+      <c r="D45" s="24">
         <f>$D$11*D40/100*D41/60*$D$20</f>
         <v/>
       </c>
-      <c r="E45" s="25">
+      <c r="E45" s="24">
         <f>$D$11*E40/100*E41/60*$D$20</f>
         <v/>
       </c>
-      <c r="F45" s="25">
+      <c r="F45" s="24">
         <f>$D$11*F40/100*F41/60*$D$20</f>
         <v/>
       </c>
-      <c r="G45" s="25">
+      <c r="G45" s="24">
         <f>$D$11*G40/100*G41/60*$D$20</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="22" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>Declined-case cost per month</t>
         </is>
       </c>
-      <c r="B46" s="23" t="inlineStr">
+      <c r="B46" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
+      <c r="C46" s="23" t="inlineStr">
         <is>
           <t>Cases per month, times the share declined, times manual minutes, at the reviewer rate.</t>
         </is>
       </c>
-      <c r="D46" s="25">
+      <c r="D46" s="24">
         <f>$D$11*D42/100*D43/60*$D$21</f>
         <v/>
       </c>
-      <c r="E46" s="25">
+      <c r="E46" s="24">
         <f>$D$11*E42/100*E43/60*$D$21</f>
         <v/>
       </c>
-      <c r="F46" s="25">
+      <c r="F46" s="24">
         <f>$D$11*F42/100*F43/60*$D$21</f>
         <v/>
       </c>
-      <c r="G46" s="25">
+      <c r="G46" s="24">
         <f>$D$11*G42/100*G43/60*$D$21</f>
         <v/>
       </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n"/>
+      <c r="B47" s="1" t="n"/>
+      <c r="C47" s="1" t="n"/>
+      <c r="D47" s="1" t="n"/>
+      <c r="E47" s="1" t="n"/>
+      <c r="F47" s="1" t="n"/>
+      <c r="G47" s="1" t="n"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
@@ -1847,10 +2105,10 @@
           <t>Tracing, logging, the eval runner, the dashboards. Licence fees or the compute to run your own.</t>
         </is>
       </c>
-      <c r="D49" s="21" t="n"/>
-      <c r="E49" s="21" t="n"/>
-      <c r="F49" s="21" t="n"/>
-      <c r="G49" s="21" t="n"/>
+      <c r="D49" s="20" t="n"/>
+      <c r="E49" s="20" t="n"/>
+      <c r="F49" s="20" t="n"/>
+      <c r="G49" s="20" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
@@ -1868,10 +2126,10 @@
           <t>Engineering days a month spent adding cases to the eval set and fixing the ones that go stale.</t>
         </is>
       </c>
-      <c r="D50" s="21" t="n"/>
-      <c r="E50" s="21" t="n"/>
-      <c r="F50" s="21" t="n"/>
-      <c r="G50" s="21" t="n"/>
+      <c r="D50" s="20" t="n"/>
+      <c r="E50" s="20" t="n"/>
+      <c r="F50" s="20" t="n"/>
+      <c r="G50" s="20" t="n"/>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
@@ -1889,10 +2147,10 @@
           <t>Engineering days a YEAR spent re-running the eval set after a model or SDK update. Spread across the months by the model. Count every update the provider ships.</t>
         </is>
       </c>
-      <c r="D51" s="21" t="n"/>
-      <c r="E51" s="21" t="n"/>
-      <c r="F51" s="21" t="n"/>
-      <c r="G51" s="21" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="20" t="n"/>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
@@ -1910,10 +2168,10 @@
           <t>Engineering days a month spent checking that a prompt change did not break something that used to work.</t>
         </is>
       </c>
-      <c r="D52" s="21" t="n"/>
-      <c r="E52" s="21" t="n"/>
-      <c r="F52" s="21" t="n"/>
-      <c r="G52" s="21" t="n"/>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="20" t="n"/>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="20" t="n"/>
     </row>
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="26" t="inlineStr">
@@ -1931,43 +2189,52 @@
           <t>Engineering days a month on incidents caused by the system. Take it from the on-call log.</t>
         </is>
       </c>
-      <c r="D53" s="21" t="n"/>
-      <c r="E53" s="21" t="n"/>
-      <c r="F53" s="21" t="n"/>
-      <c r="G53" s="21" t="n"/>
+      <c r="D53" s="20" t="n"/>
+      <c r="E53" s="20" t="n"/>
+      <c r="F53" s="20" t="n"/>
+      <c r="G53" s="20" t="n"/>
     </row>
     <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="22" t="inlineStr">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>Upkeep cost per month</t>
         </is>
       </c>
-      <c r="B54" s="23" t="inlineStr">
+      <c r="B54" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C54" s="24" t="inlineStr">
+      <c r="C54" s="23" t="inlineStr">
         <is>
           <t>Tooling, plus every engineering day above at the day rate, with the yearly line divided by twelve.</t>
         </is>
       </c>
-      <c r="D54" s="25">
+      <c r="D54" s="24">
         <f>D49+(D50+D51/12+D52+D53)*$D$19</f>
         <v/>
       </c>
-      <c r="E54" s="25">
+      <c r="E54" s="24">
         <f>E49+(E50+E51/12+E52+E53)*$D$19</f>
         <v/>
       </c>
-      <c r="F54" s="25">
+      <c r="F54" s="24">
         <f>F49+(F50+F51/12+F52+F53)*$D$19</f>
         <v/>
       </c>
-      <c r="G54" s="25">
+      <c r="G54" s="24">
         <f>G49+(G50+G51/12+G52+G53)*$D$19</f>
         <v/>
       </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n"/>
+      <c r="B55" s="1" t="n"/>
+      <c r="C55" s="1" t="n"/>
+      <c r="D55" s="1" t="n"/>
+      <c r="E55" s="1" t="n"/>
+      <c r="F55" s="1" t="n"/>
+      <c r="G55" s="1" t="n"/>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="17" t="inlineStr">
@@ -2002,43 +2269,52 @@
           <t>The share of cases that meet the written definition with no rework. Measure it on the same set of cases for all four options.</t>
         </is>
       </c>
-      <c r="D57" s="21" t="n"/>
-      <c r="E57" s="21" t="n"/>
-      <c r="F57" s="21" t="n"/>
-      <c r="G57" s="21" t="n"/>
+      <c r="D57" s="20" t="n"/>
+      <c r="E57" s="20" t="n"/>
+      <c r="F57" s="20" t="n"/>
+      <c r="G57" s="20" t="n"/>
     </row>
     <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="22" t="inlineStr">
+      <c r="A58" s="21" t="inlineStr">
         <is>
           <t>Acceptable outcomes in the period</t>
         </is>
       </c>
-      <c r="B58" s="23" t="inlineStr">
+      <c r="B58" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C58" s="24" t="inlineStr">
+      <c r="C58" s="23" t="inlineStr">
         <is>
           <t>Total cases, times the acceptable-outcome rate.</t>
         </is>
       </c>
-      <c r="D58" s="25">
+      <c r="D58" s="24">
         <f>$D$15*D57/100</f>
         <v/>
       </c>
-      <c r="E58" s="25">
+      <c r="E58" s="24">
         <f>$D$15*E57/100</f>
         <v/>
       </c>
-      <c r="F58" s="25">
+      <c r="F58" s="24">
         <f>$D$15*F57/100</f>
         <v/>
       </c>
-      <c r="G58" s="25">
+      <c r="G58" s="24">
         <f>$D$15*G57/100</f>
         <v/>
       </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n"/>
+      <c r="B59" s="1" t="n"/>
+      <c r="C59" s="1" t="n"/>
+      <c r="D59" s="1" t="n"/>
+      <c r="E59" s="1" t="n"/>
+      <c r="F59" s="1" t="n"/>
+      <c r="G59" s="1" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="17" t="inlineStr">
@@ -2058,116 +2334,116 @@
       <c r="G60" s="18" t="n"/>
     </row>
     <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="22" t="inlineStr">
+      <c r="A61" s="21" t="inlineStr">
         <is>
           <t>Run cost per month</t>
         </is>
       </c>
-      <c r="B61" s="23" t="inlineStr">
+      <c r="B61" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C61" s="24" t="inlineStr">
+      <c r="C61" s="23" t="inlineStr">
         <is>
           <t>Model, tools, review, escalation, declined cases and upkeep, added up.</t>
         </is>
       </c>
-      <c r="D61" s="25">
+      <c r="D61" s="24">
         <f>D34+D35+D44+D45+D46+D54</f>
         <v/>
       </c>
-      <c r="E61" s="25">
+      <c r="E61" s="24">
         <f>E34+E35+E44+E45+E46+E54</f>
         <v/>
       </c>
-      <c r="F61" s="25">
+      <c r="F61" s="24">
         <f>F34+F35+F44+F45+F46+F54</f>
         <v/>
       </c>
-      <c r="G61" s="25">
+      <c r="G61" s="24">
         <f>G34+G35+G44+G45+G46+G54</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="22" t="inlineStr">
+      <c r="A62" s="21" t="inlineStr">
         <is>
           <t>Run cost for the period</t>
         </is>
       </c>
-      <c r="B62" s="23" t="inlineStr">
+      <c r="B62" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C62" s="24" t="inlineStr">
+      <c r="C62" s="23" t="inlineStr">
         <is>
           <t>Run cost per month, times months.</t>
         </is>
       </c>
-      <c r="D62" s="25">
+      <c r="D62" s="24">
         <f>D61*$D$12</f>
         <v/>
       </c>
-      <c r="E62" s="25">
+      <c r="E62" s="24">
         <f>E61*$D$12</f>
         <v/>
       </c>
-      <c r="F62" s="25">
+      <c r="F62" s="24">
         <f>F61*$D$12</f>
         <v/>
       </c>
-      <c r="G62" s="25">
+      <c r="G62" s="24">
         <f>G61*$D$12</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="22" t="inlineStr">
+      <c r="A63" s="21" t="inlineStr">
         <is>
           <t>Total cost for the period, build plus run</t>
         </is>
       </c>
-      <c r="B63" s="23" t="inlineStr">
+      <c r="B63" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C63" s="24" t="inlineStr">
+      <c r="C63" s="23" t="inlineStr">
         <is>
           <t>The build, paid once, plus the run cost for the period.</t>
         </is>
       </c>
-      <c r="D63" s="25">
+      <c r="D63" s="24">
         <f>D26+D62</f>
         <v/>
       </c>
-      <c r="E63" s="25">
+      <c r="E63" s="24">
         <f>E26+E62</f>
         <v/>
       </c>
-      <c r="F63" s="25">
+      <c r="F63" s="24">
         <f>F26+F62</f>
         <v/>
       </c>
-      <c r="G63" s="25">
+      <c r="G63" s="24">
         <f>G26+G62</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="22" t="inlineStr">
+      <c r="A64" s="21" t="inlineStr">
         <is>
           <t>Cost per case</t>
         </is>
       </c>
-      <c r="B64" s="23" t="inlineStr">
+      <c r="B64" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C64" s="24" t="inlineStr">
+      <c r="C64" s="23" t="inlineStr">
         <is>
           <t>Total cost divided by total cases. The wrong number to argue about on its own.</t>
         </is>
@@ -2190,17 +2466,17 @@
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="22" t="inlineStr">
+      <c r="A65" s="21" t="inlineStr">
         <is>
           <t>Cost per acceptable outcome</t>
         </is>
       </c>
-      <c r="B65" s="23" t="inlineStr">
+      <c r="B65" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C65" s="24" t="inlineStr">
+      <c r="C65" s="23" t="inlineStr">
         <is>
           <t>Total cost divided by acceptable outcomes. The number to argue about.</t>
         </is>
@@ -2223,83 +2499,83 @@
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="22" t="inlineStr">
+      <c r="A66" s="21" t="inlineStr">
         <is>
           <t>Net position against the manual baseline</t>
         </is>
       </c>
-      <c r="B66" s="23" t="inlineStr">
+      <c r="B66" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C66" s="24" t="inlineStr">
+      <c r="C66" s="23" t="inlineStr">
         <is>
           <t>Manual baseline minus total cost. Positive means the option saves money over the period.</t>
         </is>
       </c>
-      <c r="D66" s="25">
+      <c r="D66" s="24">
         <f>$D$16-D63</f>
         <v/>
       </c>
-      <c r="E66" s="25">
+      <c r="E66" s="24">
         <f>$D$16-E63</f>
         <v/>
       </c>
-      <c r="F66" s="25">
+      <c r="F66" s="24">
         <f>$D$16-F63</f>
         <v/>
       </c>
-      <c r="G66" s="25">
+      <c r="G66" s="24">
         <f>$D$16-G63</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="22" t="inlineStr">
+      <c r="A67" s="21" t="inlineStr">
         <is>
           <t>Months to break even on the build</t>
         </is>
       </c>
-      <c r="B67" s="23" t="inlineStr">
+      <c r="B67" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C67" s="24" t="inlineStr">
+      <c r="C67" s="23" t="inlineStr">
         <is>
           <t>Build cost divided by the monthly saving against doing it by hand. "Never" means the option costs more to run each month than the manual process.</t>
         </is>
       </c>
       <c r="D67" s="28">
-        <f>IF(($D$16/$D$12-D61)&lt;=0,"never",D26/($D$16/$D$12-D61))</f>
+        <f>IFERROR(IF(($D$16/$D$12-D61)&lt;=0,"never",D26/($D$16/$D$12-D61)),"")</f>
         <v/>
       </c>
       <c r="E67" s="28">
-        <f>IF(($D$16/$D$12-E61)&lt;=0,"never",E26/($D$16/$D$12-E61))</f>
+        <f>IFERROR(IF(($D$16/$D$12-E61)&lt;=0,"never",E26/($D$16/$D$12-E61)),"")</f>
         <v/>
       </c>
       <c r="F67" s="28">
-        <f>IF(($D$16/$D$12-F61)&lt;=0,"never",F26/($D$16/$D$12-F61))</f>
+        <f>IFERROR(IF(($D$16/$D$12-F61)&lt;=0,"never",F26/($D$16/$D$12-F61)),"")</f>
         <v/>
       </c>
       <c r="G67" s="28">
-        <f>IF(($D$16/$D$12-G61)&lt;=0,"never",G26/($D$16/$D$12-G61))</f>
+        <f>IFERROR(IF(($D$16/$D$12-G61)&lt;=0,"never",G26/($D$16/$D$12-G61)),"")</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="22" t="inlineStr">
+      <c r="A68" s="21" t="inlineStr">
         <is>
           <t>Cost per acceptable outcome, options that save money</t>
         </is>
       </c>
-      <c r="B68" s="23" t="inlineStr">
+      <c r="B68" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C68" s="24" t="inlineStr">
+      <c r="C68" s="23" t="inlineStr">
         <is>
           <t>Blank for an option that costs more over the period than doing it by hand.</t>
         </is>
@@ -2322,17 +2598,17 @@
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="22" t="inlineStr">
+      <c r="A69" s="21" t="inlineStr">
         <is>
           <t>Leading option</t>
         </is>
       </c>
-      <c r="B69" s="23" t="inlineStr">
+      <c r="B69" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C69" s="24" t="inlineStr">
+      <c r="C69" s="23" t="inlineStr">
         <is>
           <t>The option with the lowest cost per acceptable outcome among those that save money. The rubric on the Read me sheet says what to do with each answer.</t>
         </is>
@@ -2341,25 +2617,47 @@
         <f>IFERROR(INDEX($D$7:$G$7,MATCH(MIN(D68:G68),D68:G68,0)),"Nothing here beats doing it by hand")</f>
         <v/>
       </c>
-      <c r="E69" s="18" t="n"/>
-      <c r="F69" s="18" t="n"/>
-      <c r="G69" s="18" t="n"/>
+      <c r="E69" s="25" t="n"/>
+      <c r="F69" s="25" t="n"/>
+      <c r="G69" s="25" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n"/>
+      <c r="B70" s="1" t="n"/>
+      <c r="C70" s="1" t="n"/>
+      <c r="D70" s="1" t="n"/>
+      <c r="E70" s="1" t="n"/>
+      <c r="F70" s="1" t="n"/>
+      <c r="G70" s="1" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n"/>
+      <c r="B71" s="1" t="n"/>
+      <c r="C71" s="1" t="n"/>
+      <c r="D71" s="1" t="n"/>
+      <c r="E71" s="1" t="n"/>
+      <c r="F71" s="1" t="n"/>
+      <c r="G71" s="1" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A5:G5"/>
   </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00183D32"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2371,20 +2669,16 @@
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>● The Living Craft</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="n"/>
-      <c r="C1" s="13" t="n"/>
-      <c r="D1" s="13" t="n"/>
-      <c r="E1" s="13" t="n"/>
-      <c r="F1" s="13" t="n"/>
-      <c r="G1" s="13" t="n"/>
-    </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>The Run-Cost Model Tool</t>
@@ -2403,19 +2697,34 @@
           <t>Four ways to do the same job, costed over one period  ·  Built by Sunil Mathew, co-authored with Claude</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n"/>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="13" t="n"/>
-      <c r="G3" s="13" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="n"/>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="1" t="n"/>
+      <c r="F4" s="1" t="n"/>
+      <c r="G4" s="1" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>An ordering agent across 40 sites</t>
         </is>
       </c>
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+      <c r="E5" s="1" t="n"/>
+      <c r="F5" s="1" t="n"/>
+      <c r="G5" s="1" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -2423,6 +2732,12 @@
           <t>A retailer in India raises about 2,000 purchase orders a month across 40 sites. Each one takes a buyer 25 minutes by hand.</t>
         </is>
       </c>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="1" t="n"/>
+      <c r="E6" s="1" t="n"/>
+      <c r="F6" s="1" t="n"/>
+      <c r="G6" s="1" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -2430,6 +2745,12 @@
           <t>The team built a full agent that reads the request, checks stock and supplier terms, and places the order. It worked. It ran at ₹3.7L a month against ₹5L for the buyers, and still lost money over the year once the ₹23L build and the upkeep were counted.</t>
         </is>
       </c>
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="n"/>
+      <c r="G7" s="1" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -2437,6 +2758,12 @@
           <t>Building it forced the team to write down every decision rule the buyers had been carrying in their heads. A second rules workflow, rebuilt on that written spec, took 35 engineering days and wins on cost per acceptable outcome.</t>
         </is>
       </c>
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="n"/>
+      <c r="G8" s="1" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
@@ -2444,6 +2771,12 @@
           <t>Cost per case picks the original rules workflow. Cost per acceptable outcome picks the rebuilt one. That gap is the whole reason the second number exists.</t>
         </is>
       </c>
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="1" t="n"/>
+      <c r="D9" s="1" t="n"/>
+      <c r="E9" s="1" t="n"/>
+      <c r="F9" s="1" t="n"/>
+      <c r="G9" s="1" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -2451,13 +2784,43 @@
           <t>Every figure is in Indian rupees at Indian rates. If you work elsewhere, change the four rates in sections 1 and 2 first. The shape of the comparison holds; the absolute numbers will not.</t>
         </is>
       </c>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="1" t="n"/>
+      <c r="E10" s="1" t="n"/>
+      <c r="F10" s="1" t="n"/>
+      <c r="G10" s="1" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="1" t="n"/>
+      <c r="E11" s="1" t="n"/>
+      <c r="F11" s="1" t="n"/>
+      <c r="G11" s="1" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Fill the yellow cells. Column C says what to type and where the number comes from. Grey rows are worked out for you; do not type into them. Percent lines take a percentage: 12 means 12%.</t>
-        </is>
-      </c>
+          <t>Fill the sand-coloured cells. Column C says what to type and where the number comes from. Pale green rows are worked out for you; do not type into them. Percent lines take a percentage: 12 means 12%.</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="1" t="n"/>
+      <c r="D13" s="1" t="n"/>
+      <c r="E13" s="1" t="n"/>
+      <c r="F13" s="1" t="n"/>
+      <c r="G13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -2497,6 +2860,9 @@
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="n"/>
       <c r="D15" s="16" t="inlineStr">
         <is>
           <t>Plain code, from the rules the team already knew.</t>
@@ -2541,7 +2907,7 @@
           <t>Currency label</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>free text</t>
         </is>
@@ -2556,6 +2922,9 @@
           <t>INR</t>
         </is>
       </c>
+      <c r="E17" s="1" t="n"/>
+      <c r="F17" s="1" t="n"/>
+      <c r="G17" s="1" t="n"/>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -2573,9 +2942,12 @@
           <t>One case is one unit of work: a purchase order, a ticket, a refund request. Take the count from last quarter, not from the plan.</t>
         </is>
       </c>
-      <c r="D18" s="21" t="n">
+      <c r="D18" s="20" t="n">
         <v>2000</v>
       </c>
+      <c r="E18" s="1" t="n"/>
+      <c r="F18" s="1" t="n"/>
+      <c r="G18" s="1" t="n"/>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -2593,9 +2965,12 @@
           <t>The window the build has to pay for itself. Twelve is the usual budget horizon. Make it longer only if you can defend the longer horizon in the room.</t>
         </is>
       </c>
-      <c r="D19" s="21" t="n">
+      <c r="D19" s="20" t="n">
         <v>12</v>
       </c>
+      <c r="E19" s="1" t="n"/>
+      <c r="F19" s="1" t="n"/>
+      <c r="G19" s="1" t="n"/>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -2613,9 +2988,12 @@
           <t>How long one person takes to finish one case today. Time it on ten real cases.</t>
         </is>
       </c>
-      <c r="D20" s="21" t="n">
+      <c r="D20" s="20" t="n">
         <v>25</v>
       </c>
+      <c r="E20" s="1" t="n"/>
+      <c r="F20" s="1" t="n"/>
+      <c r="G20" s="1" t="n"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -2633,57 +3011,69 @@
           <t>Fully loaded: salary, benefits, seat. Use the rate of the people who actually do the work today.</t>
         </is>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="20" t="n">
         <v>600</v>
       </c>
+      <c r="E21" s="1" t="n"/>
+      <c r="F21" s="1" t="n"/>
+      <c r="G21" s="1" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>Total cases in the period</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>Cases per month multiplied by months.</t>
         </is>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="24">
         <f>$D$18*$D$19</f>
         <v/>
       </c>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
-      <c r="G22" s="18" t="n"/>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="25" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>Manual baseline cost for the period</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>Total cases, times minutes per case, times the hourly rate. This is the number every option has to beat.</t>
         </is>
       </c>
-      <c r="D23" s="25">
+      <c r="D23" s="24">
         <f>$D$22*$D$20/60*$D$21</f>
         <v/>
       </c>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="25" t="n"/>
+      <c r="G23" s="25" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="1" t="n"/>
+      <c r="C24" s="1" t="n"/>
+      <c r="D24" s="1" t="n"/>
+      <c r="E24" s="1" t="n"/>
+      <c r="F24" s="1" t="n"/>
+      <c r="G24" s="1" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
@@ -2718,9 +3108,12 @@
           <t>What one engineer-day costs you. Used for the build and for upkeep.</t>
         </is>
       </c>
-      <c r="D26" s="21" t="n">
+      <c r="D26" s="20" t="n">
         <v>20000</v>
       </c>
+      <c r="E26" s="1" t="n"/>
+      <c r="F26" s="1" t="n"/>
+      <c r="G26" s="1" t="n"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -2738,9 +3131,12 @@
           <t>Used for escalations: the cases an engineer has to look at.</t>
         </is>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D27" s="20" t="n">
         <v>2500</v>
       </c>
+      <c r="E27" s="1" t="n"/>
+      <c r="F27" s="1" t="n"/>
+      <c r="G27" s="1" t="n"/>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -2758,9 +3154,21 @@
           <t>Used for reviewing output and for finishing declined cases by hand. Often the same rate as the manual baseline.</t>
         </is>
       </c>
-      <c r="D28" s="21" t="n">
+      <c r="D28" s="20" t="n">
         <v>600</v>
       </c>
+      <c r="E28" s="1" t="n"/>
+      <c r="F28" s="1" t="n"/>
+      <c r="G28" s="1" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="1" t="n"/>
+      <c r="C29" s="1" t="n"/>
+      <c r="D29" s="1" t="n"/>
+      <c r="E29" s="1" t="n"/>
+      <c r="F29" s="1" t="n"/>
+      <c r="G29" s="1" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
@@ -2795,16 +3203,16 @@
           <t>From the first line of code to a system that handles real cases. Include integration with the tools it calls.</t>
         </is>
       </c>
-      <c r="D31" s="21" t="n">
+      <c r="D31" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="E31" s="21" t="n">
+      <c r="E31" s="20" t="n">
         <v>35</v>
       </c>
-      <c r="F31" s="21" t="n">
+      <c r="F31" s="20" t="n">
         <v>45</v>
       </c>
-      <c r="G31" s="21" t="n">
+      <c r="G31" s="20" t="n">
         <v>95</v>
       </c>
     </row>
@@ -2824,51 +3232,60 @@
           <t>An eval is a set of real cases with known-correct answers that the system is scored against. Building one is engineering time.</t>
         </is>
       </c>
-      <c r="D32" s="21" t="n">
+      <c r="D32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="21" t="n">
+      <c r="E32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="21" t="n">
+      <c r="F32" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="G32" s="21" t="n">
+      <c r="G32" s="20" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>Total build cost</t>
         </is>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>Build days plus eval days, times the engineering day rate.</t>
         </is>
       </c>
-      <c r="D33" s="25">
+      <c r="D33" s="24">
         <f>(D31+D32)*$D$26</f>
         <v/>
       </c>
-      <c r="E33" s="25">
+      <c r="E33" s="24">
         <f>(E31+E32)*$D$26</f>
         <v/>
       </c>
-      <c r="F33" s="25">
+      <c r="F33" s="24">
         <f>(F31+F32)*$D$26</f>
         <v/>
       </c>
-      <c r="G33" s="25">
+      <c r="G33" s="24">
         <f>(G31+G32)*$D$26</f>
         <v/>
       </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n"/>
+      <c r="B34" s="1" t="n"/>
+      <c r="C34" s="1" t="n"/>
+      <c r="D34" s="1" t="n"/>
+      <c r="E34" s="1" t="n"/>
+      <c r="F34" s="1" t="n"/>
+      <c r="G34" s="1" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="17" t="inlineStr">
@@ -2903,16 +3320,16 @@
           <t>How many times a case calls the model when everything works. An agent that plans, then acts, then checks its work makes several.</t>
         </is>
       </c>
-      <c r="D36" s="21" t="n">
+      <c r="D36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="21" t="n">
+      <c r="E36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="21" t="n">
+      <c r="F36" s="20" t="n">
         <v>1.2</v>
       </c>
-      <c r="G36" s="21" t="n">
+      <c r="G36" s="20" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2932,16 +3349,16 @@
           <t>Total model calls divided by successful ones. Count timeouts, tool errors and loops that re-enter, not only refusals. 1.0 means the system never retries, which no real system does.</t>
         </is>
       </c>
-      <c r="D37" s="21" t="n">
+      <c r="D37" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E37" s="21" t="n">
+      <c r="E37" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="21" t="n">
+      <c r="F37" s="20" t="n">
         <v>1.15</v>
       </c>
-      <c r="G37" s="21" t="n">
+      <c r="G37" s="20" t="n">
         <v>1.35</v>
       </c>
     </row>
@@ -2961,16 +3378,16 @@
           <t>Average cost of one call, including the input tokens. Take it from a month of real invoices, not from the price list.</t>
         </is>
       </c>
-      <c r="D38" s="21" t="n">
+      <c r="D38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="21" t="n">
+      <c r="E38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="21" t="n">
+      <c r="F38" s="20" t="n">
         <v>1.8</v>
       </c>
-      <c r="G38" s="21" t="n">
+      <c r="G38" s="20" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -2990,16 +3407,16 @@
           <t>Lookups, searches, writes to other systems. Anything with a price per call or a rate limit.</t>
         </is>
       </c>
-      <c r="D39" s="21" t="n">
+      <c r="D39" s="20" t="n">
         <v>0.2</v>
       </c>
-      <c r="E39" s="21" t="n">
+      <c r="E39" s="20" t="n">
         <v>0.2</v>
       </c>
-      <c r="F39" s="21" t="n">
+      <c r="F39" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="21" t="n">
+      <c r="G39" s="20" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3019,84 +3436,93 @@
           <t>Average across the tools it calls. Internal calls are not free: price the compute.</t>
         </is>
       </c>
-      <c r="D40" s="21" t="n">
+      <c r="D40" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="E40" s="21" t="n">
+      <c r="E40" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="F40" s="21" t="n">
+      <c r="F40" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="G40" s="21" t="n">
+      <c r="G40" s="20" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="22" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>Model cost per month</t>
         </is>
       </c>
-      <c r="B41" s="23" t="inlineStr">
+      <c r="B41" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C41" s="24" t="inlineStr">
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>Cases per month, times calls per case, times the retry multiplier, times the cost per call.</t>
         </is>
       </c>
-      <c r="D41" s="25">
+      <c r="D41" s="24">
         <f>$D$18*D36*D37*D38</f>
         <v/>
       </c>
-      <c r="E41" s="25">
+      <c r="E41" s="24">
         <f>$D$18*E36*E37*E38</f>
         <v/>
       </c>
-      <c r="F41" s="25">
+      <c r="F41" s="24">
         <f>$D$18*F36*F37*F38</f>
         <v/>
       </c>
-      <c r="G41" s="25">
+      <c r="G41" s="24">
         <f>$D$18*G36*G37*G38</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>Tool cost per month</t>
         </is>
       </c>
-      <c r="B42" s="23" t="inlineStr">
+      <c r="B42" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C42" s="23" t="inlineStr">
         <is>
           <t>Cases per month, times tool calls per case, times the cost per tool call.</t>
         </is>
       </c>
-      <c r="D42" s="25">
+      <c r="D42" s="24">
         <f>$D$18*D39*D40</f>
         <v/>
       </c>
-      <c r="E42" s="25">
+      <c r="E42" s="24">
         <f>$D$18*E39*E40</f>
         <v/>
       </c>
-      <c r="F42" s="25">
+      <c r="F42" s="24">
         <f>$D$18*F39*F40</f>
         <v/>
       </c>
-      <c r="G42" s="25">
+      <c r="G42" s="24">
         <f>$D$18*G39*G40</f>
         <v/>
       </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n"/>
+      <c r="B43" s="1" t="n"/>
+      <c r="C43" s="1" t="n"/>
+      <c r="D43" s="1" t="n"/>
+      <c r="E43" s="1" t="n"/>
+      <c r="F43" s="1" t="n"/>
+      <c r="G43" s="1" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
@@ -3131,16 +3557,16 @@
           <t>100 for a model-assisted draft, because a person approves every one. A sample, such as 20, for a full agent.</t>
         </is>
       </c>
-      <c r="D45" s="21" t="n">
+      <c r="D45" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="E45" s="21" t="n">
+      <c r="E45" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="F45" s="21" t="n">
+      <c r="F45" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="G45" s="21" t="n">
+      <c r="G45" s="20" t="n">
         <v>20</v>
       </c>
     </row>
@@ -3160,16 +3586,16 @@
           <t>Time it on real cases. Approving a good draft is quick; checking an agent that acted on its own is not.</t>
         </is>
       </c>
-      <c r="D46" s="21" t="n">
+      <c r="D46" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="E46" s="21" t="n">
+      <c r="E46" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="F46" s="21" t="n">
+      <c r="F46" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="G46" s="21" t="n">
+      <c r="G46" s="20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3189,16 +3615,16 @@
           <t>Cases that stop and need somebody who can read the trace. Measure it in a trial. A demo will show you 0.</t>
         </is>
       </c>
-      <c r="D47" s="21" t="n">
+      <c r="D47" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E47" s="21" t="n">
+      <c r="E47" s="20" t="n">
         <v>0.8</v>
       </c>
-      <c r="F47" s="21" t="n">
+      <c r="F47" s="20" t="n">
         <v>1.5</v>
       </c>
-      <c r="G47" s="21" t="n">
+      <c r="G47" s="20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3218,16 +3644,16 @@
           <t>Reading the trace, working out what happened, fixing the case. Longer for an agent, because there is more trace to read.</t>
         </is>
       </c>
-      <c r="D48" s="21" t="n">
+      <c r="D48" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="E48" s="21" t="n">
+      <c r="E48" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="F48" s="21" t="n">
+      <c r="F48" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="G48" s="21" t="n">
+      <c r="G48" s="20" t="n">
         <v>35</v>
       </c>
     </row>
@@ -3247,16 +3673,16 @@
           <t>Cases the system refuses or gives up on. They do not disappear: a person finishes them, at the manual rate.</t>
         </is>
       </c>
-      <c r="D49" s="21" t="n">
+      <c r="D49" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="E49" s="21" t="n">
+      <c r="E49" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="F49" s="21" t="n">
+      <c r="F49" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="G49" s="21" t="n">
+      <c r="G49" s="20" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3276,117 +3702,126 @@
           <t>Usually close to the manual baseline, because the person starts from nothing.</t>
         </is>
       </c>
-      <c r="D50" s="21" t="n">
+      <c r="D50" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="E50" s="21" t="n">
+      <c r="E50" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="F50" s="21" t="n">
+      <c r="F50" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="G50" s="21" t="n">
+      <c r="G50" s="20" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="22" t="inlineStr">
+      <c r="A51" s="21" t="inlineStr">
         <is>
           <t>Review cost per month</t>
         </is>
       </c>
-      <c r="B51" s="23" t="inlineStr">
+      <c r="B51" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C51" s="24" t="inlineStr">
+      <c r="C51" s="23" t="inlineStr">
         <is>
           <t>Cases per month, times the share reviewed, times minutes per review, at the reviewer rate.</t>
         </is>
       </c>
-      <c r="D51" s="25">
+      <c r="D51" s="24">
         <f>$D$18*D45/100*D46/60*$D$28</f>
         <v/>
       </c>
-      <c r="E51" s="25">
+      <c r="E51" s="24">
         <f>$D$18*E45/100*E46/60*$D$28</f>
         <v/>
       </c>
-      <c r="F51" s="25">
+      <c r="F51" s="24">
         <f>$D$18*F45/100*F46/60*$D$28</f>
         <v/>
       </c>
-      <c r="G51" s="25">
+      <c r="G51" s="24">
         <f>$D$18*G45/100*G46/60*$D$28</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="A52" s="21" t="inlineStr">
         <is>
           <t>Escalation cost per month</t>
         </is>
       </c>
-      <c r="B52" s="23" t="inlineStr">
+      <c r="B52" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C52" s="24" t="inlineStr">
+      <c r="C52" s="23" t="inlineStr">
         <is>
           <t>Cases per month, times the share escalated, times minutes per escalation, at the engineer rate.</t>
         </is>
       </c>
-      <c r="D52" s="25">
+      <c r="D52" s="24">
         <f>$D$18*D47/100*D48/60*$D$27</f>
         <v/>
       </c>
-      <c r="E52" s="25">
+      <c r="E52" s="24">
         <f>$D$18*E47/100*E48/60*$D$27</f>
         <v/>
       </c>
-      <c r="F52" s="25">
+      <c r="F52" s="24">
         <f>$D$18*F47/100*F48/60*$D$27</f>
         <v/>
       </c>
-      <c r="G52" s="25">
+      <c r="G52" s="24">
         <f>$D$18*G47/100*G48/60*$D$27</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="22" t="inlineStr">
+      <c r="A53" s="21" t="inlineStr">
         <is>
           <t>Declined-case cost per month</t>
         </is>
       </c>
-      <c r="B53" s="23" t="inlineStr">
+      <c r="B53" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C53" s="24" t="inlineStr">
+      <c r="C53" s="23" t="inlineStr">
         <is>
           <t>Cases per month, times the share declined, times manual minutes, at the reviewer rate.</t>
         </is>
       </c>
-      <c r="D53" s="25">
+      <c r="D53" s="24">
         <f>$D$18*D49/100*D50/60*$D$28</f>
         <v/>
       </c>
-      <c r="E53" s="25">
+      <c r="E53" s="24">
         <f>$D$18*E49/100*E50/60*$D$28</f>
         <v/>
       </c>
-      <c r="F53" s="25">
+      <c r="F53" s="24">
         <f>$D$18*F49/100*F50/60*$D$28</f>
         <v/>
       </c>
-      <c r="G53" s="25">
+      <c r="G53" s="24">
         <f>$D$18*G49/100*G50/60*$D$28</f>
         <v/>
       </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n"/>
+      <c r="B54" s="1" t="n"/>
+      <c r="C54" s="1" t="n"/>
+      <c r="D54" s="1" t="n"/>
+      <c r="E54" s="1" t="n"/>
+      <c r="F54" s="1" t="n"/>
+      <c r="G54" s="1" t="n"/>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="17" t="inlineStr">
@@ -3421,16 +3856,16 @@
           <t>Tracing, logging, the eval runner, the dashboards. Licence fees or the compute to run your own.</t>
         </is>
       </c>
-      <c r="D56" s="21" t="n">
+      <c r="D56" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="21" t="n">
+      <c r="E56" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F56" s="21" t="n">
+      <c r="F56" s="20" t="n">
         <v>8000</v>
       </c>
-      <c r="G56" s="21" t="n">
+      <c r="G56" s="20" t="n">
         <v>35000</v>
       </c>
     </row>
@@ -3450,16 +3885,16 @@
           <t>Engineering days a month spent adding cases to the eval set and fixing the ones that go stale.</t>
         </is>
       </c>
-      <c r="D57" s="21" t="n">
+      <c r="D57" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E57" s="21" t="n">
+      <c r="E57" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F57" s="21" t="n">
+      <c r="F57" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G57" s="21" t="n">
+      <c r="G57" s="20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3479,16 +3914,16 @@
           <t>Engineering days a YEAR spent re-running the eval set after a model or SDK update. Spread across the months by the model. Count every update the provider ships.</t>
         </is>
       </c>
-      <c r="D58" s="21" t="n">
+      <c r="D58" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E58" s="21" t="n">
+      <c r="E58" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F58" s="21" t="n">
+      <c r="F58" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="G58" s="21" t="n">
+      <c r="G58" s="20" t="n">
         <v>24</v>
       </c>
     </row>
@@ -3508,16 +3943,16 @@
           <t>Engineering days a month spent checking that a prompt change did not break something that used to work.</t>
         </is>
       </c>
-      <c r="D59" s="21" t="n">
+      <c r="D59" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E59" s="21" t="n">
+      <c r="E59" s="20" t="n">
         <v>0.25</v>
       </c>
-      <c r="F59" s="21" t="n">
+      <c r="F59" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="G59" s="21" t="n">
+      <c r="G59" s="20" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -3537,51 +3972,60 @@
           <t>Engineering days a month on incidents caused by the system. Take it from the on-call log.</t>
         </is>
       </c>
-      <c r="D60" s="21" t="n">
+      <c r="D60" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="21" t="n">
+      <c r="E60" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F60" s="21" t="n">
+      <c r="F60" s="20" t="n">
         <v>0.25</v>
       </c>
-      <c r="G60" s="21" t="n">
+      <c r="G60" s="20" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="22" t="inlineStr">
+      <c r="A61" s="21" t="inlineStr">
         <is>
           <t>Upkeep cost per month</t>
         </is>
       </c>
-      <c r="B61" s="23" t="inlineStr">
+      <c r="B61" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C61" s="24" t="inlineStr">
+      <c r="C61" s="23" t="inlineStr">
         <is>
           <t>Tooling, plus every engineering day above at the day rate, with the yearly line divided by twelve.</t>
         </is>
       </c>
-      <c r="D61" s="25">
+      <c r="D61" s="24">
         <f>D56+(D57+D58/12+D59+D60)*$D$26</f>
         <v/>
       </c>
-      <c r="E61" s="25">
+      <c r="E61" s="24">
         <f>E56+(E57+E58/12+E59+E60)*$D$26</f>
         <v/>
       </c>
-      <c r="F61" s="25">
+      <c r="F61" s="24">
         <f>F56+(F57+F58/12+F59+F60)*$D$26</f>
         <v/>
       </c>
-      <c r="G61" s="25">
+      <c r="G61" s="24">
         <f>G56+(G57+G58/12+G59+G60)*$D$26</f>
         <v/>
       </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n"/>
+      <c r="B62" s="1" t="n"/>
+      <c r="C62" s="1" t="n"/>
+      <c r="D62" s="1" t="n"/>
+      <c r="E62" s="1" t="n"/>
+      <c r="F62" s="1" t="n"/>
+      <c r="G62" s="1" t="n"/>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="17" t="inlineStr">
@@ -3616,51 +4060,60 @@
           <t>The share of cases that meet the written definition with no rework. Measure it on the same set of cases for all four options.</t>
         </is>
       </c>
-      <c r="D64" s="21" t="n">
+      <c r="D64" s="20" t="n">
         <v>78</v>
       </c>
-      <c r="E64" s="21" t="n">
+      <c r="E64" s="20" t="n">
         <v>91</v>
       </c>
-      <c r="F64" s="21" t="n">
+      <c r="F64" s="20" t="n">
         <v>89</v>
       </c>
-      <c r="G64" s="21" t="n">
+      <c r="G64" s="20" t="n">
         <v>94</v>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="22" t="inlineStr">
+      <c r="A65" s="21" t="inlineStr">
         <is>
           <t>Acceptable outcomes in the period</t>
         </is>
       </c>
-      <c r="B65" s="23" t="inlineStr">
+      <c r="B65" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C65" s="24" t="inlineStr">
+      <c r="C65" s="23" t="inlineStr">
         <is>
           <t>Total cases, times the acceptable-outcome rate.</t>
         </is>
       </c>
-      <c r="D65" s="25">
+      <c r="D65" s="24">
         <f>$D$22*D64/100</f>
         <v/>
       </c>
-      <c r="E65" s="25">
+      <c r="E65" s="24">
         <f>$D$22*E64/100</f>
         <v/>
       </c>
-      <c r="F65" s="25">
+      <c r="F65" s="24">
         <f>$D$22*F64/100</f>
         <v/>
       </c>
-      <c r="G65" s="25">
+      <c r="G65" s="24">
         <f>$D$22*G64/100</f>
         <v/>
       </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n"/>
+      <c r="B66" s="1" t="n"/>
+      <c r="C66" s="1" t="n"/>
+      <c r="D66" s="1" t="n"/>
+      <c r="E66" s="1" t="n"/>
+      <c r="F66" s="1" t="n"/>
+      <c r="G66" s="1" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="17" t="inlineStr">
@@ -3680,116 +4133,116 @@
       <c r="G67" s="18" t="n"/>
     </row>
     <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="22" t="inlineStr">
+      <c r="A68" s="21" t="inlineStr">
         <is>
           <t>Run cost per month</t>
         </is>
       </c>
-      <c r="B68" s="23" t="inlineStr">
+      <c r="B68" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C68" s="24" t="inlineStr">
+      <c r="C68" s="23" t="inlineStr">
         <is>
           <t>Model, tools, review, escalation, declined cases and upkeep, added up.</t>
         </is>
       </c>
-      <c r="D68" s="25">
+      <c r="D68" s="24">
         <f>D41+D42+D51+D52+D53+D61</f>
         <v/>
       </c>
-      <c r="E68" s="25">
+      <c r="E68" s="24">
         <f>E41+E42+E51+E52+E53+E61</f>
         <v/>
       </c>
-      <c r="F68" s="25">
+      <c r="F68" s="24">
         <f>F41+F42+F51+F52+F53+F61</f>
         <v/>
       </c>
-      <c r="G68" s="25">
+      <c r="G68" s="24">
         <f>G41+G42+G51+G52+G53+G61</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="22" t="inlineStr">
+      <c r="A69" s="21" t="inlineStr">
         <is>
           <t>Run cost for the period</t>
         </is>
       </c>
-      <c r="B69" s="23" t="inlineStr">
+      <c r="B69" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C69" s="24" t="inlineStr">
+      <c r="C69" s="23" t="inlineStr">
         <is>
           <t>Run cost per month, times months.</t>
         </is>
       </c>
-      <c r="D69" s="25">
+      <c r="D69" s="24">
         <f>D68*$D$19</f>
         <v/>
       </c>
-      <c r="E69" s="25">
+      <c r="E69" s="24">
         <f>E68*$D$19</f>
         <v/>
       </c>
-      <c r="F69" s="25">
+      <c r="F69" s="24">
         <f>F68*$D$19</f>
         <v/>
       </c>
-      <c r="G69" s="25">
+      <c r="G69" s="24">
         <f>G68*$D$19</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="22" t="inlineStr">
+      <c r="A70" s="21" t="inlineStr">
         <is>
           <t>Total cost for the period, build plus run</t>
         </is>
       </c>
-      <c r="B70" s="23" t="inlineStr">
+      <c r="B70" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C70" s="24" t="inlineStr">
+      <c r="C70" s="23" t="inlineStr">
         <is>
           <t>The build, paid once, plus the run cost for the period.</t>
         </is>
       </c>
-      <c r="D70" s="25">
+      <c r="D70" s="24">
         <f>D33+D69</f>
         <v/>
       </c>
-      <c r="E70" s="25">
+      <c r="E70" s="24">
         <f>E33+E69</f>
         <v/>
       </c>
-      <c r="F70" s="25">
+      <c r="F70" s="24">
         <f>F33+F69</f>
         <v/>
       </c>
-      <c r="G70" s="25">
+      <c r="G70" s="24">
         <f>G33+G69</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="22" t="inlineStr">
+      <c r="A71" s="21" t="inlineStr">
         <is>
           <t>Cost per case</t>
         </is>
       </c>
-      <c r="B71" s="23" t="inlineStr">
+      <c r="B71" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C71" s="24" t="inlineStr">
+      <c r="C71" s="23" t="inlineStr">
         <is>
           <t>Total cost divided by total cases. The wrong number to argue about on its own.</t>
         </is>
@@ -3812,17 +4265,17 @@
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="22" t="inlineStr">
+      <c r="A72" s="21" t="inlineStr">
         <is>
           <t>Cost per acceptable outcome</t>
         </is>
       </c>
-      <c r="B72" s="23" t="inlineStr">
+      <c r="B72" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C72" s="24" t="inlineStr">
+      <c r="C72" s="23" t="inlineStr">
         <is>
           <t>Total cost divided by acceptable outcomes. The number to argue about.</t>
         </is>
@@ -3845,83 +4298,83 @@
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="22" t="inlineStr">
+      <c r="A73" s="21" t="inlineStr">
         <is>
           <t>Net position against the manual baseline</t>
         </is>
       </c>
-      <c r="B73" s="23" t="inlineStr">
+      <c r="B73" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C73" s="24" t="inlineStr">
+      <c r="C73" s="23" t="inlineStr">
         <is>
           <t>Manual baseline minus total cost. Positive means the option saves money over the period.</t>
         </is>
       </c>
-      <c r="D73" s="25">
+      <c r="D73" s="24">
         <f>$D$23-D70</f>
         <v/>
       </c>
-      <c r="E73" s="25">
+      <c r="E73" s="24">
         <f>$D$23-E70</f>
         <v/>
       </c>
-      <c r="F73" s="25">
+      <c r="F73" s="24">
         <f>$D$23-F70</f>
         <v/>
       </c>
-      <c r="G73" s="25">
+      <c r="G73" s="24">
         <f>$D$23-G70</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="22" t="inlineStr">
+      <c r="A74" s="21" t="inlineStr">
         <is>
           <t>Months to break even on the build</t>
         </is>
       </c>
-      <c r="B74" s="23" t="inlineStr">
+      <c r="B74" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C74" s="24" t="inlineStr">
+      <c r="C74" s="23" t="inlineStr">
         <is>
           <t>Build cost divided by the monthly saving against doing it by hand. "Never" means the option costs more to run each month than the manual process.</t>
         </is>
       </c>
       <c r="D74" s="28">
-        <f>IF(($D$23/$D$19-D68)&lt;=0,"never",D33/($D$23/$D$19-D68))</f>
+        <f>IFERROR(IF(($D$23/$D$19-D68)&lt;=0,"never",D33/($D$23/$D$19-D68)),"")</f>
         <v/>
       </c>
       <c r="E74" s="28">
-        <f>IF(($D$23/$D$19-E68)&lt;=0,"never",E33/($D$23/$D$19-E68))</f>
+        <f>IFERROR(IF(($D$23/$D$19-E68)&lt;=0,"never",E33/($D$23/$D$19-E68)),"")</f>
         <v/>
       </c>
       <c r="F74" s="28">
-        <f>IF(($D$23/$D$19-F68)&lt;=0,"never",F33/($D$23/$D$19-F68))</f>
+        <f>IFERROR(IF(($D$23/$D$19-F68)&lt;=0,"never",F33/($D$23/$D$19-F68)),"")</f>
         <v/>
       </c>
       <c r="G74" s="28">
-        <f>IF(($D$23/$D$19-G68)&lt;=0,"never",G33/($D$23/$D$19-G68))</f>
+        <f>IFERROR(IF(($D$23/$D$19-G68)&lt;=0,"never",G33/($D$23/$D$19-G68)),"")</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="22" t="inlineStr">
+      <c r="A75" s="21" t="inlineStr">
         <is>
           <t>Cost per acceptable outcome, options that save money</t>
         </is>
       </c>
-      <c r="B75" s="23" t="inlineStr">
+      <c r="B75" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C75" s="24" t="inlineStr">
+      <c r="C75" s="23" t="inlineStr">
         <is>
           <t>Blank for an option that costs more over the period than doing it by hand.</t>
         </is>
@@ -3944,17 +4397,17 @@
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="22" t="inlineStr">
+      <c r="A76" s="21" t="inlineStr">
         <is>
           <t>Leading option</t>
         </is>
       </c>
-      <c r="B76" s="23" t="inlineStr">
+      <c r="B76" s="22" t="inlineStr">
         <is>
           <t>worked out</t>
         </is>
       </c>
-      <c r="C76" s="24" t="inlineStr">
+      <c r="C76" s="23" t="inlineStr">
         <is>
           <t>The option with the lowest cost per acceptable outcome among those that save money. The rubric on the Read me sheet says what to do with each answer.</t>
         </is>
@@ -3963,9 +4416,27 @@
         <f>IFERROR(INDEX($D$14:$G$14,MATCH(MIN(D75:G75),D75:G75,0)),"Nothing here beats doing it by hand")</f>
         <v/>
       </c>
-      <c r="E76" s="18" t="n"/>
-      <c r="F76" s="18" t="n"/>
-      <c r="G76" s="18" t="n"/>
+      <c r="E76" s="25" t="n"/>
+      <c r="F76" s="25" t="n"/>
+      <c r="G76" s="25" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n"/>
+      <c r="B77" s="1" t="n"/>
+      <c r="C77" s="1" t="n"/>
+      <c r="D77" s="1" t="n"/>
+      <c r="E77" s="1" t="n"/>
+      <c r="F77" s="1" t="n"/>
+      <c r="G77" s="1" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n"/>
+      <c r="B78" s="1" t="n"/>
+      <c r="C78" s="1" t="n"/>
+      <c r="D78" s="1" t="n"/>
+      <c r="E78" s="1" t="n"/>
+      <c r="F78" s="1" t="n"/>
+      <c r="G78" s="1" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3976,6 +4447,9 @@
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>